--- a/artfynd/A 35034-2026 artfynd.xlsx
+++ b/artfynd/A 35034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365574</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136356182</v>
       </c>
       <c r="B4" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136356241</v>
       </c>
       <c r="B5" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35034-2026 artfynd.xlsx
+++ b/artfynd/A 35034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35034-2026 artfynd.xlsx
+++ b/artfynd/A 35034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365574</v>
       </c>
       <c r="B3" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136356182</v>
       </c>
       <c r="B4" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136356241</v>
       </c>
       <c r="B5" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35034-2026 artfynd.xlsx
+++ b/artfynd/A 35034-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
